--- a/MainTop/12.03.2026 Таня Озон/print_print_sorted.xlsx
+++ b/MainTop/12.03.2026 Таня Озон/print_print_sorted.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\12.03.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E19CC22-0C3E-4E55-B5D4-B76BAB7FD394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3596B8F-794F-465E-8DCB-A10DECA518CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -700,11 +700,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.42578125" customWidth="1"/>
-    <col min="2" max="8" width="5.28515625" customWidth="1"/>
+    <col min="2" max="7" width="13.85546875" customWidth="1"/>
+    <col min="8" max="8" width="5.28515625" customWidth="1"/>
     <col min="9" max="9" width="5.140625" customWidth="1"/>
     <col min="10" max="10" width="20" customWidth="1"/>
     <col min="11" max="11" width="5.140625" customWidth="1"/>
@@ -3685,6 +3686,46 @@
         <v>3</v>
       </c>
     </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B86">
+        <f>SUM(B2:B85)</f>
+        <v>53</v>
+      </c>
+      <c r="C86">
+        <f t="shared" ref="C86:G86" si="0">SUM(C2:C85)</f>
+        <v>54</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="0"/>
+        <v>115</v>
+      </c>
+      <c r="E86">
+        <f t="shared" si="0"/>
+        <v>81</v>
+      </c>
+      <c r="F86">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="G86">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="H86">
+        <f>SUM(H2:H85)</f>
+        <v>548</v>
+      </c>
+      <c r="K86">
+        <f>SUM(K2:K85)</f>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H87">
+        <f>H86-K86</f>
+        <v>383</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
